--- a/products-import.xlsx
+++ b/products-import.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K301"/>
+  <dimension ref="A1:K555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11173,6 +11173,8896 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 155/70 R13 летняя</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>204000</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Damas, Matiz</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>TR-0001</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Damas, Matiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Шина Hankook 155/70 R13 летняя</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>314000</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Damas, Matiz</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>TR-0002</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Damas, Matiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Шина Michelin 155/70 R13 летняя</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>549000</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Damas, Matiz</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>TR-0003</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Damas, Matiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Шина Sailun 165/70 R14 летняя</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>259000</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Sailun</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>TR-0004</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Spark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Шина Nexen 165/70 R14 летняя</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>399000</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>TR-0005</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Spark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Шина Continental 165/70 R14 летняя</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>698000</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>TR-0006</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Spark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Шина Linglong 175/70 R14 летняя</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>290000</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Nexia 2, Cobalt (база)</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Linglong</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>TR-0007</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Nexia 2, Cobalt (база).</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Шина Kumho 175/70 R14 летняя</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>446000</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Nexia 2, Cobalt (база)</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>TR-0008</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Nexia 2, Cobalt (база).</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 175/70 R14 летняя</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>781000</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Nexia 2, Cobalt (база)</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>TR-0009</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Nexia 2, Cobalt (база).</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Шина Triangle 185/65 R14 летняя</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>346000</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Nexia 2, Lacetti</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>TR-0010</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Nexia 2, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Шина Hankook 185/65 R14 летняя</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>532000</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Nexia 2, Lacetti</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>TR-0011</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Nexia 2, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Шина Michelin 185/65 R14 летняя</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>931000</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Nexia 2, Lacetti</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>TR-0012</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Nexia 2, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 185/60 R15 летняя</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>395000</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>TR-0013</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Cobalt, Nexia 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Шина Nexen 185/60 R15 летняя</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>608000</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>TR-0014</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Cobalt, Nexia 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Шина Continental 185/60 R15 летняя</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>1064000</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>TR-0015</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Cobalt, Nexia 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Шина Sailun 195/65 R15 летняя</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>445000</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3, Gentra</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Sailun</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>TR-0016</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Cobalt, Nexia 3, Gentra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Шина Kumho 195/65 R15 летняя</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>684000</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3, Gentra</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>TR-0017</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Cobalt, Nexia 3, Gentra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 195/65 R15 летняя</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>1197000</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3, Gentra</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>TR-0018</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Cobalt, Nexia 3, Gentra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Шина Linglong 195/55 R16 летняя</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>531000</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Gentra, Lacetti</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Linglong</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>TR-0019</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Gentra, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Шина Hankook 195/55 R16 летняя</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>817000</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Gentra, Lacetti</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>TR-0020</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Gentra, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Шина Michelin 195/55 R16 летняя</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Gentra, Lacetti</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>TR-0021</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Gentra, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Шина Triangle 205/55 R16 летняя</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>556000</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Malibu 1, Onix</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>TR-0022</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Malibu 1, Onix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Шина Nexen 205/55 R16 летняя</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>855000</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Malibu 1, Onix</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>TR-0023</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Malibu 1, Onix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Шина Continental 205/55 R16 летняя</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>1496000</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Malibu 1, Onix</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>TR-0024</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Malibu 1, Onix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 215/60 R16 летняя</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>618000</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Captiva, Epica</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>TR-0025</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Captiva, Epica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Шина Kumho 215/60 R16 летняя</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>950000</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Captiva, Epica</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>TR-0026</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Captiva, Epica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 215/60 R16 летняя</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>1662000</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Captiva, Epica</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>TR-0027</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Captiva, Epica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Шина Sailun 215/55 R17 летняя</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>772000</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Malibu 2</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Sailun</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>TR-0028</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Malibu 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Шина Hankook 215/55 R17 летняя</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>1188000</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Malibu 2</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>TR-0029</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Malibu 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Шина Michelin 215/55 R17 летняя</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>2078000</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Malibu 2</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>TR-0030</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Malibu 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Шина Linglong 225/55 R17 летняя</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>834000</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Malibu 2, Camry</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Linglong</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>TR-0031</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Malibu 2, Camry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Шина Nexen 225/55 R17 летняя</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>1282000</v>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Malibu 2, Camry</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>TR-0032</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Malibu 2, Camry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Шина Continental 225/55 R17 летняя</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>2244000</v>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Malibu 2, Camry</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>TR-0033</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Malibu 2, Camry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Шина Sailun 155/70 R13 всесезонная</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>214000</v>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Damas, Matiz</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Sailun</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>TR-0034</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Damas, Matiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Шина Nexen 155/70 R13 всесезонная</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>330000</v>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Damas, Matiz</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>TR-0035</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Damas, Matiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Шина Continental 155/70 R13 всесезонная</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>578000</v>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Damas, Matiz</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>TR-0036</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Damas, Matiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Шина Linglong 165/70 R14 всесезонная</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>273000</v>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Linglong</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>TR-0037</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Spark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Шина Kumho 165/70 R14 всесезонная</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>420000</v>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>TR-0038</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Spark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 165/70 R14 всесезонная</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>735000</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>TR-0039</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Spark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Шина Triangle 175/70 R14 всесезонная</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>306000</v>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Nexia 2, Cobalt (база)</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>TR-0040</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Nexia 2, Cobalt (база).</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Шина Hankook 175/70 R14 всесезонная</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>470000</v>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Nexia 2, Cobalt (база)</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>TR-0041</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Nexia 2, Cobalt (база).</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Шина Michelin 175/70 R14 всесезонная</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>822000</v>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Nexia 2, Cobalt (база)</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>TR-0042</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Nexia 2, Cobalt (база).</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 185/65 R14 всесезонная</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>364000</v>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Nexia 2, Lacetti</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>TR-0043</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Nexia 2, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Шина Nexen 185/65 R14 всесезонная</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>560000</v>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Nexia 2, Lacetti</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>TR-0044</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Nexia 2, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Шина Continental 185/65 R14 всесезонная</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>980000</v>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Nexia 2, Lacetti</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>TR-0045</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Nexia 2, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Шина Sailun 185/60 R15 всесезонная</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>416000</v>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Sailun</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>TR-0046</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Cobalt, Nexia 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Шина Kumho 185/60 R15 всесезонная</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>640000</v>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>TR-0047</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Cobalt, Nexia 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 185/60 R15 всесезонная</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>TR-0048</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Cobalt, Nexia 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Шина Linglong 195/65 R15 всесезонная</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>468000</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3, Gentra</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Linglong</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>TR-0049</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Cobalt, Nexia 3, Gentra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Шина Hankook 195/65 R15 всесезонная</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>720000</v>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3, Gentra</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>TR-0050</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Cobalt, Nexia 3, Gentra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Шина Michelin 195/65 R15 всесезонная</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>1260000</v>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3, Gentra</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>TR-0051</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Cobalt, Nexia 3, Gentra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Шина Triangle 195/55 R16 всесезонная</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>559000</v>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Gentra, Lacetti</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>TR-0052</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Gentra, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Шина Nexen 195/55 R16 всесезонная</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>860000</v>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Gentra, Lacetti</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>TR-0053</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Gentra, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Шина Continental 195/55 R16 всесезонная</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>1505000</v>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Gentra, Lacetti</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>TR-0054</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Gentra, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 205/55 R16 всесезонная</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>585000</v>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Malibu 1, Onix</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>TR-0055</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Malibu 1, Onix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Шина Kumho 205/55 R16 всесезонная</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>900000</v>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Malibu 1, Onix</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>TR-0056</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Malibu 1, Onix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 205/55 R16 всесезонная</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Malibu 1, Onix</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>TR-0057</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Malibu 1, Onix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Шина Sailun 215/60 R16 всесезонная</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>650000</v>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Captiva, Epica</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Sailun</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>TR-0058</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Captiva, Epica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Шина Hankook 215/60 R16 всесезонная</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Captiva, Epica</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>TR-0059</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Captiva, Epica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Шина Michelin 215/60 R16 всесезонная</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Captiva, Epica</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>TR-0060</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Captiva, Epica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Шина Linglong 215/55 R17 всесезонная</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>812000</v>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Malibu 2</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Linglong</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>TR-0061</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Malibu 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Шина Nexen 215/55 R17 всесезонная</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Malibu 2</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>TR-0062</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Malibu 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Шина Continental 215/55 R17 всесезонная</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>2188000</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Malibu 2</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>TR-0063</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Malibu 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Шина Triangle 225/55 R17 всесезонная</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>878000</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Malibu 2, Camry</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>TR-0064</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Malibu 2, Camry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Шина Kumho 225/55 R17 всесезонная</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Malibu 2, Camry</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>TR-0065</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Malibu 2, Camry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 225/55 R17 всесезонная</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>2362000</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Malibu 2, Camry</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>TR-0066</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Malibu 2, Camry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Шина Linglong 155/70 R13 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Damas, Matiz</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Linglong</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>TR-0067</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Damas, Matiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Шина Kumho 155/70 R13 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>370000</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Damas, Matiz</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>TR-0068</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Damas, Matiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 155/70 R13 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>647000</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Damas, Matiz</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>TR-0069</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Damas, Matiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Шина Triangle 165/70 R14 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>306000</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>TR-0070</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Spark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Шина Hankook 165/70 R14 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>470000</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>TR-0071</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Spark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Шина Michelin 165/70 R14 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>823000</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>TR-0072</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Spark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 175/70 R14 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>342000</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Nexia 2, Cobalt (база)</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>TR-0073</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Nexia 2, Cobalt (база).</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Шина Nexen 175/70 R14 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>526000</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Nexia 2, Cobalt (база)</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>TR-0074</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Nexia 2, Cobalt (база).</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Шина Continental 175/70 R14 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>921000</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Nexia 2, Cobalt (база)</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>TR-0075</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Nexia 2, Cobalt (база).</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Шина Sailun 185/65 R14 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>408000</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Nexia 2, Lacetti</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Sailun</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>TR-0076</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Nexia 2, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Шина Kumho 185/65 R14 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>627000</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Nexia 2, Lacetti</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>TR-0077</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Nexia 2, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 185/65 R14 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>1098000</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Nexia 2, Lacetti</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>TR-0078</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Nexia 2, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Шина Linglong 185/60 R15 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>466000</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Linglong</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>TR-0079</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Cobalt, Nexia 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Шина Hankook 185/60 R15 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>717000</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>TR-0080</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Cobalt, Nexia 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Шина Michelin 185/60 R15 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>1254000</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>TR-0081</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Cobalt, Nexia 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Шина Triangle 195/65 R15 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>524000</v>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3, Gentra</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>TR-0082</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Cobalt, Nexia 3, Gentra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Шина Nexen 195/65 R15 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>806000</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3, Gentra</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>TR-0083</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Cobalt, Nexia 3, Gentra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Шина Continental 195/65 R15 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>1411000</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3, Gentra</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>TR-0084</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Cobalt, Nexia 3, Gentra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 195/55 R16 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>626000</v>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Gentra, Lacetti</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>TR-0085</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Gentra, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Шина Kumho 195/55 R16 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>963000</v>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Gentra, Lacetti</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>TR-0086</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Gentra, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 195/55 R16 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>1686000</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Gentra, Lacetti</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>TR-0087</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Gentra, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Шина Sailun 205/55 R16 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>655000</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Malibu 1, Onix</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Sailun</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>TR-0088</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Malibu 1, Onix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Шина Hankook 205/55 R16 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>1008000</v>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Malibu 1, Onix</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>TR-0089</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Malibu 1, Onix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Шина Michelin 205/55 R16 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>1764000</v>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Malibu 1, Onix</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>TR-0090</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Malibu 1, Onix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Шина Linglong 215/60 R16 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>728000</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Captiva, Epica</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Linglong</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>TR-0091</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Captiva, Epica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Шина Nexen 215/60 R16 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Captiva, Epica</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>TR-0092</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Captiva, Epica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Шина Continental 215/60 R16 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>1960000</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Captiva, Epica</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>TR-0093</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Captiva, Epica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Шина Triangle 215/55 R17 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>910000</v>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Malibu 2</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>TR-0094</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Malibu 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Шина Kumho 215/55 R17 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Malibu 2</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>TR-0095</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Malibu 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 215/55 R17 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Malibu 2</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>TR-0096</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Malibu 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 225/55 R17 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>983000</v>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Malibu 2, Camry</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>TR-0097</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Malibu 2, Camry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Шина Hankook 225/55 R17 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>1512000</v>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Malibu 2, Camry</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>TR-0098</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Malibu 2, Camry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Шина Michelin 225/55 R17 зимняя нешипованная</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>2646000</v>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Malibu 2, Camry</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>TR-0099</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Malibu 2, Camry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Шина Triangle 155/70 R13 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>257000</v>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Damas, Matiz</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>TR-0100</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Damas, Matiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Шина Hankook 155/70 R13 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>396000</v>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Damas, Matiz</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>TR-0101</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Damas, Matiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Шина Michelin 155/70 R13 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>693000</v>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Damas, Matiz</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>TR-0102</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Damas, Matiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 165/70 R14 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>328000</v>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>TR-0103</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Spark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Шина Nexen 165/70 R14 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>504000</v>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>TR-0104</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Spark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Шина Continental 165/70 R14 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>882000</v>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>TR-0105</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Spark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Шина Sailun 175/70 R14 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>367000</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Nexia 2, Cobalt (база)</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Sailun</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>TR-0106</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Nexia 2, Cobalt (база).</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Шина Kumho 175/70 R14 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>564000</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Nexia 2, Cobalt (база)</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>TR-0107</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Nexia 2, Cobalt (база).</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 175/70 R14 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>987000</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Nexia 2, Cobalt (база)</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>TR-0108</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Nexia 2, Cobalt (база).</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Шина Linglong 185/65 R14 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>437000</v>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Nexia 2, Lacetti</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Linglong</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>TR-0109</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Nexia 2, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Шина Hankook 185/65 R14 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>672000</v>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Nexia 2, Lacetti</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>TR-0110</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Nexia 2, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Шина Michelin 185/65 R14 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>1176000</v>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Nexia 2, Lacetti</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>TR-0111</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Nexia 2, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Шина Triangle 185/60 R15 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>499000</v>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>TR-0112</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Cobalt, Nexia 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Шина Nexen 185/60 R15 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>768000</v>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>TR-0113</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Cobalt, Nexia 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Шина Continental 185/60 R15 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>1344000</v>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>TR-0114</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Cobalt, Nexia 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 195/65 R15 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>562000</v>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3, Gentra</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>TR-0115</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Cobalt, Nexia 3, Gentra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Шина Kumho 195/65 R15 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>864000</v>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3, Gentra</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>TR-0116</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Cobalt, Nexia 3, Gentra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 195/65 R15 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>1512000</v>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Cobalt, Nexia 3, Gentra</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>TR-0117</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Cobalt, Nexia 3, Gentra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Шина Sailun 195/55 R16 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>671000</v>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Gentra, Lacetti</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Sailun</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>TR-0118</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Gentra, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Шина Hankook 195/55 R16 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>1032000</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Gentra, Lacetti</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>TR-0119</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Gentra, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Шина Michelin 195/55 R16 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>1806000</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Gentra, Lacetti</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>TR-0120</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Gentra, Lacetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Шина Linglong 205/55 R16 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>702000</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Malibu 1, Onix</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Linglong</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>TR-0121</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Malibu 1, Onix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Шина Nexen 205/55 R16 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Malibu 1, Onix</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>TR-0122</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Malibu 1, Onix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Шина Continental 205/55 R16 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>1890000</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Malibu 1, Onix</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>TR-0123</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Malibu 1, Onix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Шина Triangle 215/60 R16 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>780000</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Captiva, Epica</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>TR-0124</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Captiva, Epica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Шина Kumho 215/60 R16 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Captiva, Epica</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>TR-0125</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Captiva, Epica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 215/60 R16 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Captiva, Epica</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>TR-0126</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Captiva, Epica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 215/55 R17 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>975000</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Malibu 2</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>TR-0127</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Malibu 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Шина Hankook 215/55 R17 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Malibu 2</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>TR-0128</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Malibu 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Шина Michelin 215/55 R17 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>2625000</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Malibu 2</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>TR-0129</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Malibu 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Шина Sailun 225/55 R17 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>1053000</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Malibu 2, Camry</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Sailun</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>TR-0130</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Malibu 2, Camry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Шина Nexen 225/55 R17 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>1620000</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Malibu 2, Camry</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>TR-0131</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Malibu 2, Camry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Шина Continental 225/55 R17 зимняя шипованная</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>tires_car</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>2835000</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Malibu 2, Camry</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>TR-0132</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Malibu 2, Camry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Шина Sailun 215/65 R16 летняя</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>648000</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Tracker, Duster</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Sailun</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>TR-0133</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Tracker, Duster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Шина Nexen 215/65 R16 летняя</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>998000</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Tracker, Duster</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>TR-0134</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Tracker, Duster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Шина Continental 215/65 R16 летняя</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>1746000</v>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Tracker, Duster</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>TR-0135</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Tracker, Duster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Шина Linglong 225/65 R17 летняя</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>834000</v>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Equinox, Tucson</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Linglong</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>TR-0136</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Equinox, Tucson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Шина Kumho 225/65 R17 летняя</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>1282000</v>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Equinox, Tucson</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>TR-0137</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Equinox, Tucson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 225/65 R17 летняя</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>2244000</v>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Equinox, Tucson</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>TR-0138</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Equinox, Tucson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Шина Triangle 235/65 R17 летняя</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>895000</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Captiva, Sorento</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>TR-0139</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Captiva, Sorento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Шина Hankook 235/65 R17 летняя</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>1378000</v>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Captiva, Sorento</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>TR-0140</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Captiva, Sorento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Шина Michelin 235/65 R17 летняя</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>2411000</v>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Captiva, Sorento</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>TR-0141</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Captiva, Sorento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 225/60 R18 летняя</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>988000</v>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Tracker 2, Sportage</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>TR-0142</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Tracker 2, Sportage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Шина Nexen 225/60 R18 летняя</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>1520000</v>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Tracker 2, Sportage</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>TR-0143</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Tracker 2, Sportage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Шина Continental 225/60 R18 летняя</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>2660000</v>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Tracker 2, Sportage</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>TR-0144</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Tracker 2, Sportage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Шина Sailun 235/55 R19 летняя</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>1297000</v>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Tahoe, Traverse</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Sailun</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>TR-0145</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Tahoe, Traverse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Шина Kumho 235/55 R19 летняя</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>1995000</v>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Tahoe, Traverse</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>TR-0146</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Tahoe, Traverse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 235/55 R19 летняя</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>3491000</v>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Tahoe, Traverse</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>TR-0147</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Tahoe, Traverse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Шина Linglong 215/65 R16 всесезонная</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>682000</v>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Tracker, Duster</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Linglong</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>TR-0148</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Tracker, Duster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Шина Kumho 215/65 R16 всесезонная</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Tracker, Duster</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>TR-0149</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Tracker, Duster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 215/65 R16 всесезонная</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>1838000</v>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Tracker, Duster</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>TR-0150</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Tracker, Duster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Шина Triangle 225/65 R17 всесезонная</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>878000</v>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Equinox, Tucson</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>TR-0151</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Equinox, Tucson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Шина Hankook 225/65 R17 всесезонная</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Equinox, Tucson</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>TR-0152</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Equinox, Tucson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Шина Michelin 225/65 R17 всесезонная</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>2362000</v>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Equinox, Tucson</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>TR-0153</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Equinox, Tucson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 235/65 R17 всесезонная</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>942000</v>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Captiva, Sorento</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>TR-0154</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Captiva, Sorento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Шина Nexen 235/65 R17 всесезонная</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Captiva, Sorento</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>TR-0155</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Captiva, Sorento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Шина Continental 235/65 R17 всесезонная</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>2538000</v>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Captiva, Sorento</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>TR-0156</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Captiva, Sorento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Шина Sailun 225/60 R18 всесезонная</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>1040000</v>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Tracker 2, Sportage</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Sailun</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>TR-0157</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Tracker 2, Sportage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Шина Kumho 225/60 R18 всесезонная</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Tracker 2, Sportage</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>TR-0158</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Tracker 2, Sportage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 225/60 R18 всесезонная</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Tracker 2, Sportage</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>TR-0159</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Tracker 2, Sportage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Шина Linglong 235/55 R19 всесезонная</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>1365000</v>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Tahoe, Traverse</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Linglong</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>TR-0160</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Tahoe, Traverse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Шина Hankook 235/55 R19 всесезонная</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Tahoe, Traverse</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>TR-0161</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Tahoe, Traverse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Шина Michelin 235/55 R19 всесезонная</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>3675000</v>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Tahoe, Traverse</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>TR-0162</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Tahoe, Traverse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Шина Triangle 215/65 R16 зимняя</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>785000</v>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Tracker, Duster</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>TR-0163</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Tracker, Duster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Шина Hankook 215/65 R16 зимняя</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>1208000</v>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Tracker, Duster</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>TR-0164</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Tracker, Duster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Шина Michelin 215/65 R16 зимняя</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>2113000</v>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Tracker, Duster</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>TR-0165</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Tracker, Duster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 225/65 R17 зимняя</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>1009000</v>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Equinox, Tucson</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>TR-0166</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Equinox, Tucson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Шина Nexen 225/65 R17 зимняя</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>1552000</v>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Equinox, Tucson</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>TR-0167</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Equinox, Tucson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Шина Continental 225/65 R17 зимняя</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>2717000</v>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Equinox, Tucson</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>TR-0168</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Equinox, Tucson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Шина Sailun 235/65 R17 зимняя</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>1084000</v>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Captiva, Sorento</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Sailun</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>TR-0169</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Captiva, Sorento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Шина Kumho 235/65 R17 зимняя</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>1667000</v>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Captiva, Sorento</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>TR-0170</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Captiva, Sorento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 235/65 R17 зимняя</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>2918000</v>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Captiva, Sorento</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>TR-0171</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Captiva, Sorento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Шина Linglong 225/60 R18 зимняя</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>1196000</v>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Tracker 2, Sportage</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Linglong</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>TR-0172</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Tracker 2, Sportage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Шина Hankook 225/60 R18 зимняя</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>1840000</v>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Tracker 2, Sportage</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Hankook</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>TR-0173</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Tracker 2, Sportage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Шина Michelin 225/60 R18 зимняя</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>3220000</v>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Tracker 2, Sportage</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>TR-0174</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Tracker 2, Sportage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Шина Triangle 235/55 R19 зимняя</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>1570000</v>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Tahoe, Traverse</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>TR-0175</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Tahoe, Traverse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Шина Nexen 235/55 R19 зимняя</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>2415000</v>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Tahoe, Traverse</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Nexen</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>TR-0176</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Tahoe, Traverse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Шина Continental 235/55 R19 зимняя</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>tires_suv</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>4226000</v>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Tahoe, Traverse</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>TR-0177</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Tahoe, Traverse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 235/75 R15 A/T</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>910000</v>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Нива, УАЗ</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>TR-0178</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Нива, УАЗ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Шина Kumho 235/75 R15 A/T</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Нива, УАЗ</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>TR-0179</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Нива, УАЗ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Шина BFGoodrich 235/75 R15 A/T</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>2080000</v>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Нива, УАЗ</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>BFGoodrich</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>TR-0180</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Нива, УАЗ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 235/75 R15 M/T</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>1138000</v>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Нива, УАЗ</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>TR-0181</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Нива, УАЗ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Шина Kumho 235/75 R15 M/T</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>1625000</v>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Нива, УАЗ</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>TR-0182</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Нива, УАЗ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Шина BFGoodrich 235/75 R15 M/T</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Нива, УАЗ</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>BFGoodrich</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>TR-0183</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Нива, УАЗ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 245/70 R16 A/T</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>1155000</v>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Pajero, Prado</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>TR-0184</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Pajero, Prado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Шина Kumho 245/70 R16 A/T</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Pajero, Prado</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>TR-0185</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Pajero, Prado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Шина BFGoodrich 245/70 R16 A/T</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Pajero, Prado</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>BFGoodrich</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>TR-0186</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Pajero, Prado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 245/70 R16 M/T</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>1444000</v>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Pajero, Prado</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>TR-0187</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Pajero, Prado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Шина Kumho 245/70 R16 M/T</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>2062000</v>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Pajero, Prado</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>TR-0188</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Pajero, Prado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Шина BFGoodrich 245/70 R16 M/T</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Pajero, Prado</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>BFGoodrich</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>TR-0189</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Pajero, Prado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 265/65 R17 A/T</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>1365000</v>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Prado, Hilux</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>TR-0190</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Prado, Hilux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Шина Kumho 265/65 R17 A/T</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>1950000</v>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Prado, Hilux</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>TR-0191</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Prado, Hilux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Шина BFGoodrich 265/65 R17 A/T</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>3120000</v>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Prado, Hilux</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>BFGoodrich</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>TR-0192</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Prado, Hilux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 265/65 R17 M/T</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>1706000</v>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Prado, Hilux</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>TR-0193</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Prado, Hilux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Шина Kumho 265/65 R17 M/T</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>2438000</v>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Prado, Hilux</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>TR-0194</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Prado, Hilux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Шина BFGoodrich 265/65 R17 M/T</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>3900000</v>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Prado, Hilux</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>BFGoodrich</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>TR-0195</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Prado, Hilux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 265/70 R16 A/T</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>1330000</v>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Hilux, Land Cruiser</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>TR-0196</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Hilux, Land Cruiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Шина Kumho 265/70 R16 A/T</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Hilux, Land Cruiser</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>TR-0197</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Hilux, Land Cruiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Шина BFGoodrich 265/70 R16 A/T</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>3040000</v>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Hilux, Land Cruiser</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>BFGoodrich</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>TR-0198</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Hilux, Land Cruiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 265/70 R16 M/T</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>1662000</v>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Hilux, Land Cruiser</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>TR-0199</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Hilux, Land Cruiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Шина Kumho 265/70 R16 M/T</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>2375000</v>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Hilux, Land Cruiser</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>TR-0200</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Hilux, Land Cruiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Шина BFGoodrich 265/70 R16 M/T</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Hilux, Land Cruiser</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>BFGoodrich</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>TR-0201</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Hilux, Land Cruiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 285/60 R18 A/T</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Land Cruiser</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>TR-0202</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Land Cruiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Шина Kumho 285/60 R18 A/T</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Land Cruiser</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>TR-0203</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Land Cruiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Шина BFGoodrich 285/60 R18 A/T</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Land Cruiser</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>BFGoodrich</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>TR-0204</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Land Cruiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Шина Kapsen 285/60 R18 M/T</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>2188000</v>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Land Cruiser</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Kapsen</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>TR-0205</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Land Cruiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Шина Kumho 285/60 R18 M/T</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>3125000</v>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Land Cruiser</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>TR-0206</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Land Cruiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Шина BFGoodrich 285/60 R18 M/T</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>tires_offroad</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Land Cruiser</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>BFGoodrich</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>TR-0207</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Land Cruiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 205/55 R16 Run-flat летняя</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>tires_rf</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>BMW 3, Mini</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>TR-0208</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: BMW 3, Mini.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Шина Continental 205/55 R16 Run-flat летняя</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>tires_rf</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>1890000</v>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>BMW 3, Mini</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>TR-0209</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: BMW 3, Mini.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 225/45 R17 Run-flat летняя</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>tires_rf</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>BMW 3</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>TR-0210</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: BMW 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Шина Continental 225/45 R17 Run-flat летняя</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>tires_rf</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>2205000</v>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>BMW 3</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>TR-0211</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: BMW 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Шина Bridgestone 245/45 R18 Run-flat летняя</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>tires_rf</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>BMW 5, Mercedes E</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>TR-0212</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: BMW 5, Mercedes E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Шина Continental 245/45 R18 Run-flat летняя</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>tires_rf</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>2835000</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>BMW 5, Mercedes E</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>TR-0213</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: BMW 5, Mercedes E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Шина Triangle 155 R13C (лёгкогрузовая)</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>tires_lt</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>315000</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Damas, Labo</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>TR-0214</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Damas, Labo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Шина Kumho 155 R13C (лёгкогрузовая)</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>tires_lt</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>420000</v>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Damas, Labo</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>TR-0215</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Damas, Labo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Шина Michelin 155 R13C (лёгкогрузовая)</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>tires_lt</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>672000</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Damas, Labo</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>TR-0216</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Damas, Labo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Шина Triangle 185/75 R16C (лёгкогрузовая)</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>tires_lt</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>638000</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Газель, Porter</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>TR-0217</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Газель, Porter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Шина Kumho 185/75 R16C (лёгкогрузовая)</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>tires_lt</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>850000</v>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Газель, Porter</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>TR-0218</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Газель, Porter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Шина Michelin 185/75 R16C (лёгкогрузовая)</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>tires_lt</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Газель, Porter</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>TR-0219</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Газель, Porter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Шина Triangle 195/70 R15C (лёгкогрузовая)</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>tires_lt</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>675000</v>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Hyundai Porter, H-1</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>TR-0220</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Hyundai Porter, H-1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Шина Kumho 195/70 R15C (лёгкогрузовая)</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>tires_lt</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>900000</v>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Hyundai Porter, H-1</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>TR-0221</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Hyundai Porter, H-1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Шина Michelin 195/70 R15C (лёгкогрузовая)</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>tires_lt</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Hyundai Porter, H-1</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>TR-0222</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Hyundai Porter, H-1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Шина Triangle 215/65 R16C (лёгкогрузовая)</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>tires_lt</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>862000</v>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Sprinter, Transit</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>TR-0223</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Sprinter, Transit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Шина Kumho 215/65 R16C (лёгкогрузовая)</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>tires_lt</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Sprinter, Transit</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>TR-0224</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Sprinter, Transit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Шина Michelin 215/65 R16C (лёгкогрузовая)</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>tires_lt</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>1840000</v>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Sprinter, Transit</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>TR-0225</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Sprinter, Transit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Шина Triangle 225/70 R15C (лёгкогрузовая)</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>tires_lt</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>750000</v>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Газель Next</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Triangle</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>TR-0226</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Газель Next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Шина Kumho 225/70 R15C (лёгкогрузовая)</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>tires_lt</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Газель Next</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Kumho</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>TR-0227</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Газель Next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Шина Michelin 225/70 R15C (лёгкогрузовая)</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>tires_lt</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Газель Next</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>TR-0228</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Газель Next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Шина Aeolus 315/80 R22.5 рулевая</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>2880000</v>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Тягачи, самосвалы</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Aeolus</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>TR-0229</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Тягачи, самосвалы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Шина Kama 315/80 R22.5 рулевая</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Тягачи, самосвалы</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Kama</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>TR-0230</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Тягачи, самосвалы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Шина Michelin 315/80 R22.5 рулевая</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>6120000</v>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Тягачи, самосвалы</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>TR-0231</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Тягачи, самосвалы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Шина Aeolus 315/80 R22.5 ведущая</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>3040000</v>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Тягачи, самосвалы</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Aeolus</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>TR-0232</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Тягачи, самосвалы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Шина Kama 315/80 R22.5 ведущая</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Тягачи, самосвалы</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Kama</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>TR-0233</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Тягачи, самосвалы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Шина Michelin 315/80 R22.5 ведущая</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>6460000</v>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Тягачи, самосвалы</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>TR-0234</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Тягачи, самосвалы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Шина Aeolus 385/65 R22.5 прицепная</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Aeolus</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>TR-0235</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Прицепы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Шина Kama 385/65 R22.5 прицепная</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Kama</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>TR-0236</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Прицепы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Шина Michelin 385/65 R22.5 прицепная</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>6800000</v>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Прицепы</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>TR-0237</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Прицепы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Шина Aeolus 295/80 R22.5 универсальная</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Автобусы, Isuzu</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Aeolus</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>TR-0238</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Автобусы, Isuzu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Шина Kama 295/80 R22.5 универсальная</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Автобусы, Isuzu</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Kama</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>TR-0239</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Автобусы, Isuzu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Шина Michelin 295/80 R22.5 универсальная</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>5610000</v>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Автобусы, Isuzu</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>TR-0240</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Автобусы, Isuzu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Шина Aeolus 11.00 R20 универсальная</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>2720000</v>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>КамАЗ, МАЗ</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Aeolus</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>TR-0241</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: КамАЗ, МАЗ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Шина Kama 11.00 R20 универсальная</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>КамАЗ, МАЗ</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Kama</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>TR-0242</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: КамАЗ, МАЗ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Шина Michelin 11.00 R20 универсальная</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>5780000</v>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>КамАЗ, МАЗ</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>TR-0243</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: КамАЗ, МАЗ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Шина Aeolus 215/75 R17.5 универсальная</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>1520000</v>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Isuzu NPR, ГАЗон</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Aeolus</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>TR-0244</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>Класс: Эконом. Подходит для: Isuzu NPR, ГАЗон.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Шина Kama 215/75 R17.5 универсальная</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Isuzu NPR, ГАЗон</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Kama</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>TR-0245</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>Класс: Средний. Подходит для: Isuzu NPR, ГАЗон.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Шина Michelin 215/75 R17.5 универсальная</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>tires_truck</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>3230000</v>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Isuzu NPR, ГАЗон</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>TR-0246</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>Класс: Премиум. Подходит для: Isuzu NPR, ГАЗон.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Мотошина Michelin 110/70 R17</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>tires_moto</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>650000</v>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Мотоциклы спорт/дорожные</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>TR-0247</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>Подходит для: Мотоциклы спорт/дорожные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Мотошина Michelin 140/70 R17</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>tires_moto</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>850000</v>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Мотоциклы спорт/дорожные</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>TR-0248</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>Подходит для: Мотоциклы спорт/дорожные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Мотошина Kenda 3.00-18</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>tires_moto</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Мопеды, Минск</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Kenda</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>TR-0249</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>Подходит для: Мопеды, Минск.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Мотошина Kenda 130/60-13</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>tires_moto</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>350000</v>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Скутеры</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Kenda</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>TR-0250</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>Подходит для: Скутеры.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Шина Белшина 16.9-38 (Трактор МТЗ (задние))</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>tires_agro</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Трактор МТЗ (задние)</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Белшина</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>TR-0251</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>Подходит для: Трактор МТЗ (задние).</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Шина Белшина 11.2-20 (Трактор МТЗ (передние))</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>tires_agro</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Трактор МТЗ (передние)</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Белшина</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>TR-0252</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>Подходит для: Трактор МТЗ (передние).</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Шина Armour 6.50-10 (Погрузчик)</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>tires_agro</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>900000</v>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Погрузчик</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Armour</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>TR-0253</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>Подходит для: Погрузчик.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Шина Armour 12.5/80-18 (Экскаватор-погрузчик)</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>tires_agro</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Экскаватор-погрузчик</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Armour</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>TR-0254</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Подходит для: Экскаватор-погрузчик.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
